--- a/docs/fem/files/xslope_griffiths5_0p5.xlsx
+++ b/docs/fem/files/xslope_griffiths5_0p5.xlsx
@@ -13598,10 +13598,10 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3">
-        <v>668300.0</v>
+        <v>2088500.0</v>
       </c>
       <c r="N11" s="3">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
